--- a/Employee_Reports_wi52/Nathaniel Laguidao Gamosa Q0418.xlsx
+++ b/Employee_Reports_wi52/Nathaniel Laguidao Gamosa Q0418.xlsx
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
